--- a/excel/Nordstreet Rima.xlsx
+++ b/excel/Nordstreet Rima.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Nordstreet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Nordstreet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A5180B-4553-4B4D-B961-26797A170A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F86A774-BA2C-4555-9C0A-36400B9341A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apžvalga" sheetId="1" r:id="rId1"/>
@@ -1248,11 +1248,11 @@
       </c>
       <c r="J3" s="8">
         <f ca="1">'Mozūriškių g. 17-3, Vilnius'!B13</f>
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="K3" s="8">
         <f ca="1">'Mozūriškių g. 17-3, Vilnius'!S3</f>
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="L3" s="5">
         <f>'Mozūriškių g. 17-3, Vilnius'!N3</f>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>26.940000000000055</v>
+        <v>29.990000000000009</v>
       </c>
       <c r="S3" s="5">
         <f t="shared" ref="S3" si="0">SUM(L3:L27)</f>
@@ -1284,23 +1284,23 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M27)</f>
-        <v>43.08</v>
+        <v>46.129999999999995</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>695.94</v>
+        <v>698.99</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>75.940000000000055</v>
+        <v>78.990000000000009</v>
       </c>
       <c r="W3" s="16">
         <f>(U3-O3)/O3</f>
-        <v>0.12248387096774202</v>
+        <v>0.12740322580645164</v>
       </c>
       <c r="X3" s="16">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.17106860280036923</v>
+        <v>0.15879907011985778</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Mozūriškių g. 17-3, Vilnius'!AA2</f>
@@ -1345,11 +1345,11 @@
       </c>
       <c r="J4" s="8">
         <f ca="1">'Birstyčios g. 27, Vilnius (11)'!B13</f>
-        <v>-23</v>
+        <v>-53</v>
       </c>
       <c r="K4" s="8">
         <f ca="1">'Birstyčios g. 27, Vilnius (11)'!S3</f>
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="L4" s="5">
         <f>'Birstyčios g. 27, Vilnius (11)'!N3</f>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="J5" s="8">
         <f ca="1">'Baltų Avenue (2)'!B13</f>
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="K5" s="8" t="str">
         <f ca="1">'Baltų Avenue (2)'!S3</f>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M5" s="5">
         <f>'Baltų Avenue (2)'!P3</f>
-        <v>3.6100000000000003</v>
+        <v>4.07</v>
       </c>
       <c r="AC5" s="5" t="str">
         <f ca="1">'Baltų Avenue (2)'!AA2</f>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="J6" s="8">
         <f ca="1">'Liepų g. 3, Vyšniūnai (6)'!B13</f>
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="K6" s="8">
         <f ca="1">'Liepų g. 3, Vyšniūnai (6)'!S3</f>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="M6" s="5">
         <f>'Liepų g. 3, Vyšniūnai (6)'!P3</f>
-        <v>4.870000000000001</v>
+        <v>7.4600000000000009</v>
       </c>
       <c r="AC6" s="5" t="str">
         <f ca="1">'Liepų g. 3, Vyšniūnai (6)'!AA2</f>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="L1" s="16">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.17106860280036923</v>
+        <v>0.15879907011985778</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3379,14 +3379,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="7">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="5">
         <f>Apžvalga!U3</f>
-        <v>695.94</v>
+        <v>698.99</v>
       </c>
     </row>
   </sheetData>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>4.870000000000001</v>
+        <v>7.4600000000000009</v>
       </c>
       <c r="Q3" s="16" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -3628,13 +3628,21 @@
       <c r="F4" s="5">
         <v>2.23</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2.23</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="J4" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K4" s="8">
+        <f t="shared" si="0"/>
+        <v>82</v>
       </c>
       <c r="Y4" s="7">
         <f t="shared" ref="Y4:Y41" si="1">J3</f>
@@ -3671,11 +3679,11 @@
       </c>
       <c r="Y5" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46258</v>
       </c>
       <c r="Z5" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -3921,7 +3929,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="D13" s="7">
         <v>46429</v>
@@ -4566,11 +4574,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>4.3900000000000006</v>
+        <v>6.620000000000001</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
-        <v>0.48</v>
+        <v>0.84</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -4795,7 +4803,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>3.6100000000000003</v>
+        <v>4.07</v>
       </c>
       <c r="Q3" s="16" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -5087,13 +5095,21 @@
       <c r="F10" s="5">
         <v>0.46</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="0"/>
+        <v>-2</v>
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="1"/>
@@ -5131,11 +5147,11 @@
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46251</v>
       </c>
       <c r="Z11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -5178,7 +5194,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="D13" s="7">
         <v>46345</v>
@@ -5907,7 +5923,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>3.6100000000000003</v>
+        <v>4.07</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
@@ -6151,7 +6167,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -6522,7 +6538,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-23</v>
+        <v>-53</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
@@ -7405,7 +7421,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -7784,7 +7800,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D13" s="7">
         <v>46284</v>
